--- a/ПР3/Backup Storage.xlsx
+++ b/ПР3/Backup Storage.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C34ABB4-1B82-483F-A17E-F557FE00BF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="2" activeTab="4" xr2:uid="{D56C4ECF-4E27-4F98-BBEF-B44C203A18B2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{D56C4ECF-4E27-4F98-BBEF-B44C203A18B2}"/>
   </bookViews>
   <sheets>
     <sheet name=" Объем запросов" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -291,39 +291,173 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="30">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -363,6 +497,93 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
@@ -373,6 +594,87 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -572,13 +874,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </left>
@@ -616,6 +911,13 @@
       </fill>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -639,6 +941,18 @@
           <bgColor theme="4"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -677,324 +991,6 @@
         <horizontal/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1060,22 +1056,22 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{03C328A3-7600-4985-9A8B-9E6F491E66BD}" name="Таблица5" displayName="Таблица5" ref="A1:E6" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{03C328A3-7600-4985-9A8B-9E6F491E66BD}" name="Таблица5" displayName="Таблица5" ref="A1:E6" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
   <autoFilter ref="A1:E6" xr:uid="{03C328A3-7600-4985-9A8B-9E6F491E66BD}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9D50F930-0B46-4708-B7B8-AE4728C4FC0C}" name="Год" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{9D50F930-0B46-4708-B7B8-AE4728C4FC0C}" name="Год" dataDxfId="19">
       <calculatedColumnFormula>A1+1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BF7E9333-5671-423F-92ED-474B1449F6B8}" name="Минимальный объем хранилища на год, ГБ" dataDxfId="10">
+    <tableColumn id="3" xr3:uid="{BF7E9333-5671-423F-92ED-474B1449F6B8}" name="Минимальный объем хранилища на год, ГБ" dataDxfId="18">
       <calculatedColumnFormula>Таблица3[[#This Row],[Минимальный объем хранилища на год, ГБ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{77A00AC5-ABD0-471D-9505-2B4898886461}" name="Необходимая скорость, Гбит/c" dataDxfId="9">
+    <tableColumn id="4" xr3:uid="{77A00AC5-ABD0-471D-9505-2B4898886461}" name="Необходимая скорость, Гбит/c" dataDxfId="17">
       <calculatedColumnFormula>8*Таблица5[[#This Row],[Минимальный объем хранилища на год, ГБ]]/$H$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D296EDFF-AD08-4EAF-8C06-E95BA3858653}" name="Необходимая скорость, МБ/c" dataDxfId="8">
+    <tableColumn id="2" xr3:uid="{D296EDFF-AD08-4EAF-8C06-E95BA3858653}" name="Необходимая скорость, МБ/c" dataDxfId="16">
       <calculatedColumnFormula>Таблица5[[#This Row],[Необходимая скорость, Гбит/c]]*128</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{81514A64-4331-46FB-8669-164BDDA2176F}" name="Минимальное колическттвол дисков" dataDxfId="7">
+    <tableColumn id="5" xr3:uid="{81514A64-4331-46FB-8669-164BDDA2176F}" name="Минимальное колическттвол дисков" dataDxfId="15">
       <calculatedColumnFormula>_xlfn.CEILING.MATH(Таблица5[[#This Row],[Необходимая скорость, МБ/c]]/$I$2,1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1084,17 +1080,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B1F05492-342A-4C7E-B397-8180F6D5BB95}" name="Таблица6" displayName="Таблица6" ref="A1:D6" totalsRowShown="0" tableBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B1F05492-342A-4C7E-B397-8180F6D5BB95}" name="Таблица6" displayName="Таблица6" ref="A1:D6" totalsRowShown="0" tableBorderDxfId="14">
   <autoFilter ref="A1:D6" xr:uid="{B1F05492-342A-4C7E-B397-8180F6D5BB95}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2CF724CA-8A89-4535-A28F-4B76B9E18E49}" name="Год" dataDxfId="18">
+    <tableColumn id="1" xr3:uid="{2CF724CA-8A89-4535-A28F-4B76B9E18E49}" name="Год" dataDxfId="13">
       <calculatedColumnFormula>A1+1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{359BBE6C-E19E-4406-AB44-1B6E3FAF8AD5}" name="Суммарный объем бэкапов (TB)" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{EDFBEEA7-C92E-4A55-9074-4039BC756481}" name="Суммарный объем бэкапов c репикацией(TB)" dataDxfId="6">
+    <tableColumn id="2" xr3:uid="{359BBE6C-E19E-4406-AB44-1B6E3FAF8AD5}" name="Суммарный объем бэкапов (TB)" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{EDFBEEA7-C92E-4A55-9074-4039BC756481}" name="Суммарный объем бэкапов c репикацией(TB)" dataDxfId="11">
       <calculatedColumnFormula>Таблица6[[#This Row],[Суммарный объем бэкапов (TB)]]*$G$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{FC5BBCF2-325A-4B43-884A-1CF3AF5A7B08}" name="Количество дисков" dataDxfId="5">
+    <tableColumn id="4" xr3:uid="{FC5BBCF2-325A-4B43-884A-1CF3AF5A7B08}" name="Количество дисков" dataDxfId="10">
       <calculatedColumnFormula>_xlfn.CEILING.MATH(C2/$F$2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1106,22 +1102,22 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{24CBF245-BDE9-4C57-B274-210639C2127C}" name="Таблица7" displayName="Таблица7" ref="A1:F6" totalsRowShown="0">
   <autoFilter ref="A1:F6" xr:uid="{24CBF245-BDE9-4C57-B274-210639C2127C}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{C0BE04AD-D800-4036-9197-44872A225E08}" name="Год" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{C0BE04AD-D800-4036-9197-44872A225E08}" name="Год" dataDxfId="29">
       <calculatedColumnFormula>A1+1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{2D787ECA-3674-4996-A74B-32A7AC30B58F}" name="Количество дисков по скорости">
       <calculatedColumnFormula>Таблица5[[#This Row],[Минимальное колическттвол дисков]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{608B01F1-5670-47B4-8A03-52629C853A7D}" name="Количество дисков по объему" dataDxfId="3">
+    <tableColumn id="3" xr3:uid="{608B01F1-5670-47B4-8A03-52629C853A7D}" name="Количество дисков по объему" dataDxfId="28">
       <calculatedColumnFormula>Таблица6[[#This Row],[Количество дисков]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CB6E3EEE-594F-4EB1-8219-6A316F97EE65}" name="Максимальное кошличество" dataDxfId="2">
+    <tableColumn id="4" xr3:uid="{CB6E3EEE-594F-4EB1-8219-6A316F97EE65}" name="Максимальное кошличество" dataDxfId="27">
       <calculatedColumnFormula>MAX(Таблица7[[#This Row],[Количество дисков по скорости]],Таблица7[[#This Row],[Количество дисков по объему]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7B9E0AE7-DFF6-4A7D-AC36-13C5B3E1093E}" name="Количество дисков на 1 ноде" dataDxfId="1">
+    <tableColumn id="5" xr3:uid="{7B9E0AE7-DFF6-4A7D-AC36-13C5B3E1093E}" name="Количество дисков на 1 ноде" dataDxfId="26">
       <calculatedColumnFormula>QUOTIENT(D2,$H$2) + _xlfn.CEILING.MATH(MOD(INT(D2),$H$2)/$H$2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{49B81C8B-9F13-49C6-997E-2A7DFF56A0A2}" name="Количество дисков" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{49B81C8B-9F13-49C6-997E-2A7DFF56A0A2}" name="Количество дисков" dataDxfId="25">
       <calculatedColumnFormula>Таблица7[[#This Row],[Количество дисков на 1 ноде]]*$H$2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1130,22 +1126,22 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{64B0AF25-7315-40B1-9762-26CBE1B2AF52}" name="Таблица4" displayName="Таблица4" ref="A1:E6" totalsRowShown="0" headerRowDxfId="20" dataDxfId="21" headerRowBorderDxfId="28" tableBorderDxfId="29" totalsRowBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{64B0AF25-7315-40B1-9762-26CBE1B2AF52}" name="Таблица4" displayName="Таблица4" ref="A1:E6" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="A1:E6" xr:uid="{64B0AF25-7315-40B1-9762-26CBE1B2AF52}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5361C555-84F8-4320-B9BF-F5EE77B58EFB}" name="Год" dataDxfId="26">
+    <tableColumn id="1" xr3:uid="{5361C555-84F8-4320-B9BF-F5EE77B58EFB}" name="Год" dataDxfId="4">
       <calculatedColumnFormula>A1+1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4BE1F316-36B0-4029-AA9B-2F60456F020C}" name="Объем горячих данных, ГБ" dataDxfId="25">
+    <tableColumn id="2" xr3:uid="{4BE1F316-36B0-4029-AA9B-2F60456F020C}" name="Объем горячих данных, ГБ" dataDxfId="3">
       <calculatedColumnFormula>Таблица3[[#This Row],[(Рост данных/месяц) в текущий год, ГБ/мес]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BDD9D6A0-DC99-4726-AFC5-BF52D22A7307}" name="Объем теплых данных, ГБ" dataDxfId="24">
+    <tableColumn id="3" xr3:uid="{BDD9D6A0-DC99-4726-AFC5-BF52D22A7307}" name="Объем теплых данных, ГБ" dataDxfId="2">
       <calculatedColumnFormula>B2*11</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{761A234F-4C93-4AE3-BD5F-7F3D3EA47276}" name="Объем холодных данных, ГБ" dataDxfId="23">
-      <calculatedColumnFormula>SUM($C$1:C2) + SUM($B$2:B1)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" xr3:uid="{AEB39C59-6A5D-4FDD-B04F-3733EA889425}" name="Минимальный объем хранилища на год, ГБ" dataDxfId="22">
+    <tableColumn id="4" xr3:uid="{761A234F-4C93-4AE3-BD5F-7F3D3EA47276}" name="Объем холодных данных, ГБ" dataDxfId="1">
+      <calculatedColumnFormula>SUM($C$1:C2) + SUM($B1:B$2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{AEB39C59-6A5D-4FDD-B04F-3733EA889425}" name="Минимальный объем хранилища на год, ГБ" dataDxfId="0">
       <calculatedColumnFormula>SUM(B2:D2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1618,7 +1614,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
-        <f t="shared" ref="A4:A67" si="2">A3+1</f>
+        <f t="shared" ref="A4:A6" si="2">A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" cm="1">
@@ -1748,11 +1744,11 @@
         <f>8*Таблица5[[#This Row],[Минимальный объем хранилища на год, ГБ]]/$H$2</f>
         <v>3.7916666666666665</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="11">
         <f>Таблица5[[#This Row],[Необходимая скорость, Гбит/c]]*128</f>
         <v>485.33333333333331</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="11">
         <f>_xlfn.CEILING.MATH(Таблица5[[#This Row],[Необходимая скорость, МБ/c]]/$I$2,1)</f>
         <v>4</v>
       </c>
@@ -1780,11 +1776,11 @@
         <f>8*Таблица5[[#This Row],[Минимальный объем хранилища на год, ГБ]]/$H$2</f>
         <v>7.9649999999999999</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="3">
         <f>Таблица5[[#This Row],[Необходимая скорость, Гбит/c]]*128</f>
         <v>1019.52</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="3">
         <f>_xlfn.CEILING.MATH(Таблица5[[#This Row],[Необходимая скорость, МБ/c]]/$I$2,1)</f>
         <v>7</v>
       </c>
@@ -1802,11 +1798,11 @@
         <f>8*Таблица5[[#This Row],[Минимальный объем хранилища на год, ГБ]]/$H$2</f>
         <v>12.558333333333334</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="3">
         <f>Таблица5[[#This Row],[Необходимая скорость, Гбит/c]]*128</f>
         <v>1607.4666666666667</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="3">
         <f>_xlfn.CEILING.MATH(Таблица5[[#This Row],[Необходимая скорость, МБ/c]]/$I$2,1)</f>
         <v>11</v>
       </c>
@@ -1824,11 +1820,11 @@
         <f>8*Таблица5[[#This Row],[Минимальный объем хранилища на год, ГБ]]/$H$2</f>
         <v>17.611666666666668</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="3">
         <f>Таблица5[[#This Row],[Необходимая скорость, Гбит/c]]*128</f>
         <v>2254.2933333333335</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="3">
         <f>_xlfn.CEILING.MATH(Таблица5[[#This Row],[Необходимая скорость, МБ/c]]/$I$2,1)</f>
         <v>16</v>
       </c>
@@ -1846,11 +1842,11 @@
         <f>8*Таблица5[[#This Row],[Минимальный объем хранилища на год, ГБ]]/$H$2</f>
         <v>23.171666666666667</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="8">
         <f>Таблица5[[#This Row],[Необходимая скорость, Гбит/c]]*128</f>
         <v>2965.9733333333334</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="8">
         <f>_xlfn.CEILING.MATH(Таблица5[[#This Row],[Необходимая скорость, МБ/c]]/$I$2,1)</f>
         <v>20</v>
       </c>
@@ -2052,7 +2048,7 @@
         <f>QUOTIENT(D2,$H$2) + _xlfn.CEILING.MATH(MOD(INT(D2),$H$2)/$H$2)</f>
         <v>2</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2">
         <f>Таблица7[[#This Row],[Количество дисков на 1 ноде]]*$H$2</f>
         <v>6</v>
       </c>
@@ -2078,10 +2074,10 @@
         <v>8</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E2:E6" si="0">QUOTIENT(D3,$H$2) + _xlfn.CEILING.MATH(MOD(INT(D3),$H$2)/$H$2)</f>
+        <f t="shared" ref="E3:E6" si="0">QUOTIENT(D3,$H$2) + _xlfn.CEILING.MATH(MOD(INT(D3),$H$2)/$H$2)</f>
         <v>3</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3">
         <f>Таблица7[[#This Row],[Количество дисков на 1 ноде]]*$H$2</f>
         <v>9</v>
       </c>
@@ -2107,7 +2103,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4">
         <f>Таблица7[[#This Row],[Количество дисков на 1 ноде]]*$H$2</f>
         <v>12</v>
       </c>
@@ -2133,7 +2129,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5">
         <f>Таблица7[[#This Row],[Количество дисков на 1 ноде]]*$H$2</f>
         <v>18</v>
       </c>
@@ -2159,7 +2155,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6">
         <f>Таблица7[[#This Row],[Количество дисков на 1 ноде]]*$H$2</f>
         <v>24</v>
       </c>

--- a/ПР3/Backup Storage.xlsx
+++ b/ПР3/Backup Storage.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Mirea\Системы хранения данных\ПР3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C34ABB4-1B82-483F-A17E-F557FE00BF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91B78A7-E2F5-4CDF-8A3A-DFAEAA398D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{D56C4ECF-4E27-4F98-BBEF-B44C203A18B2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="1" activeTab="4" xr2:uid="{D56C4ECF-4E27-4F98-BBEF-B44C203A18B2}"/>
   </bookViews>
   <sheets>
     <sheet name=" Объем запросов" sheetId="1" r:id="rId1"/>
     <sheet name="объем хранилища" sheetId="2" r:id="rId2"/>
     <sheet name="Количество дисков по скорости" sheetId="4" r:id="rId3"/>
     <sheet name="Количество дисков по объему" sheetId="5" r:id="rId4"/>
-    <sheet name="Количество дисков для кластера" sheetId="7" r:id="rId5"/>
-    <sheet name="Tiring" sheetId="3" r:id="rId6"/>
-    <sheet name="Настроки диска" sheetId="6" r:id="rId7"/>
+    <sheet name="Лист1" sheetId="8" r:id="rId5"/>
+    <sheet name="Количество дисков для кластера" sheetId="7" r:id="rId6"/>
+    <sheet name="Tiring" sheetId="3" r:id="rId7"/>
+    <sheet name="Настроки диска" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
   <si>
     <t>Количество запросов</t>
   </si>
@@ -163,13 +164,43 @@
   </si>
   <si>
     <t>Суммарный объем бэкапов c репикацией(TB)</t>
+  </si>
+  <si>
+    <t>Ценв 1 ТБ/мес</t>
+  </si>
+  <si>
+    <t>Стоимость хранения / месяц, Р/мес</t>
+  </si>
+  <si>
+    <t>Стоимость хранения / месяц, Р/год</t>
+  </si>
+  <si>
+    <t>Цена чтения, Р/ГБ</t>
+  </si>
+  <si>
+    <t>Цена 1 восстановления</t>
+  </si>
+  <si>
+    <t>Неопл объем чтения,ГБ</t>
+  </si>
+  <si>
+    <t>Количество восстановлений/год</t>
+  </si>
+  <si>
+    <t>Цена восстановлений</t>
+  </si>
+  <si>
+    <t>Стоимость хранения/год</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="#,##0.00\ &quot;₽&quot;"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,6 +224,13 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -291,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -304,11 +342,57 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="41">
+    <dxf>
+      <numFmt numFmtId="168" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -333,10 +417,8 @@
           <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
         <right/>
         <top style="thin">
           <color theme="4" tint="0.39997558519241921"/>
@@ -344,119 +426,6 @@
         <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -498,6 +467,200 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <top style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </top>
@@ -581,6 +744,55 @@
         </right>
         <top/>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -942,55 +1154,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1047,8 +1210,8 @@
     <tableColumn id="4" xr3:uid="{1DCCBF2B-8758-44B9-8FB5-6F705F1C3BCE}" name="Минимальный объем хранилища на год, ГБ">
       <calculatedColumnFormula>D1+C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{629C4D67-72FC-4A03-B2F2-9678B2E4D2ED}" name="Минимальный объем хранилища на год, ТБ">
-      <calculatedColumnFormula>_xlfn.CEILING.MATH(D2/1024,0.1)</calculatedColumnFormula>
+    <tableColumn id="5" xr3:uid="{629C4D67-72FC-4A03-B2F2-9678B2E4D2ED}" name="Минимальный объем хранилища на год, ТБ" dataDxfId="5">
+      <calculatedColumnFormula>_xlfn.CEILING.MATH(D2/1024,0.01)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1056,22 +1219,22 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{03C328A3-7600-4985-9A8B-9E6F491E66BD}" name="Таблица5" displayName="Таблица5" ref="A1:E6" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{03C328A3-7600-4985-9A8B-9E6F491E66BD}" name="Таблица5" displayName="Таблица5" ref="A1:E6" totalsRowShown="0" headerRowDxfId="40" dataDxfId="38" headerRowBorderDxfId="39" tableBorderDxfId="37" totalsRowBorderDxfId="36">
   <autoFilter ref="A1:E6" xr:uid="{03C328A3-7600-4985-9A8B-9E6F491E66BD}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9D50F930-0B46-4708-B7B8-AE4728C4FC0C}" name="Год" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{9D50F930-0B46-4708-B7B8-AE4728C4FC0C}" name="Год" dataDxfId="35">
       <calculatedColumnFormula>A1+1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BF7E9333-5671-423F-92ED-474B1449F6B8}" name="Минимальный объем хранилища на год, ГБ" dataDxfId="18">
+    <tableColumn id="3" xr3:uid="{BF7E9333-5671-423F-92ED-474B1449F6B8}" name="Минимальный объем хранилища на год, ГБ" dataDxfId="34">
       <calculatedColumnFormula>Таблица3[[#This Row],[Минимальный объем хранилища на год, ГБ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{77A00AC5-ABD0-471D-9505-2B4898886461}" name="Необходимая скорость, Гбит/c" dataDxfId="17">
+    <tableColumn id="4" xr3:uid="{77A00AC5-ABD0-471D-9505-2B4898886461}" name="Необходимая скорость, Гбит/c" dataDxfId="33">
       <calculatedColumnFormula>8*Таблица5[[#This Row],[Минимальный объем хранилища на год, ГБ]]/$H$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D296EDFF-AD08-4EAF-8C06-E95BA3858653}" name="Необходимая скорость, МБ/c" dataDxfId="16">
+    <tableColumn id="2" xr3:uid="{D296EDFF-AD08-4EAF-8C06-E95BA3858653}" name="Необходимая скорость, МБ/c" dataDxfId="32">
       <calculatedColumnFormula>Таблица5[[#This Row],[Необходимая скорость, Гбит/c]]*128</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{81514A64-4331-46FB-8669-164BDDA2176F}" name="Минимальное колическттвол дисков" dataDxfId="15">
+    <tableColumn id="5" xr3:uid="{81514A64-4331-46FB-8669-164BDDA2176F}" name="Минимальное колическттвол дисков" dataDxfId="31">
       <calculatedColumnFormula>_xlfn.CEILING.MATH(Таблица5[[#This Row],[Необходимая скорость, МБ/c]]/$I$2,1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1080,17 +1243,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B1F05492-342A-4C7E-B397-8180F6D5BB95}" name="Таблица6" displayName="Таблица6" ref="A1:D6" totalsRowShown="0" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B1F05492-342A-4C7E-B397-8180F6D5BB95}" name="Таблица6" displayName="Таблица6" ref="A1:D6" totalsRowShown="0" tableBorderDxfId="30">
   <autoFilter ref="A1:D6" xr:uid="{B1F05492-342A-4C7E-B397-8180F6D5BB95}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2CF724CA-8A89-4535-A28F-4B76B9E18E49}" name="Год" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{2CF724CA-8A89-4535-A28F-4B76B9E18E49}" name="Год" dataDxfId="29">
       <calculatedColumnFormula>A1+1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{359BBE6C-E19E-4406-AB44-1B6E3FAF8AD5}" name="Суммарный объем бэкапов (TB)" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{EDFBEEA7-C92E-4A55-9074-4039BC756481}" name="Суммарный объем бэкапов c репикацией(TB)" dataDxfId="11">
+    <tableColumn id="2" xr3:uid="{359BBE6C-E19E-4406-AB44-1B6E3FAF8AD5}" name="Суммарный объем бэкапов (TB)" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{EDFBEEA7-C92E-4A55-9074-4039BC756481}" name="Суммарный объем бэкапов c репикацией(TB)" dataDxfId="27">
       <calculatedColumnFormula>Таблица6[[#This Row],[Суммарный объем бэкапов (TB)]]*$G$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{FC5BBCF2-325A-4B43-884A-1CF3AF5A7B08}" name="Количество дисков" dataDxfId="10">
+    <tableColumn id="4" xr3:uid="{FC5BBCF2-325A-4B43-884A-1CF3AF5A7B08}" name="Количество дисков" dataDxfId="26">
       <calculatedColumnFormula>_xlfn.CEILING.MATH(C2/$F$2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1099,26 +1262,32 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{24CBF245-BDE9-4C57-B274-210639C2127C}" name="Таблица7" displayName="Таблица7" ref="A1:F6" totalsRowShown="0">
-  <autoFilter ref="A1:F6" xr:uid="{24CBF245-BDE9-4C57-B274-210639C2127C}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{C0BE04AD-D800-4036-9197-44872A225E08}" name="Год" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A39803FC-841B-4741-896F-6B50B6FB45F0}" name="Таблица8" displayName="Таблица8" ref="A1:H6" totalsRowShown="0" tableBorderDxfId="10">
+  <autoFilter ref="A1:H6" xr:uid="{A39803FC-841B-4741-896F-6B50B6FB45F0}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{C83F3DA5-2840-46A9-8BCA-9BF09606871F}" name="Год" dataDxfId="9">
       <calculatedColumnFormula>A1+1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2D787ECA-3674-4996-A74B-32A7AC30B58F}" name="Количество дисков по скорости">
-      <calculatedColumnFormula>Таблица5[[#This Row],[Минимальное колическттвол дисков]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{608B01F1-5670-47B4-8A03-52629C853A7D}" name="Количество дисков по объему" dataDxfId="28">
-      <calculatedColumnFormula>Таблица6[[#This Row],[Количество дисков]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{CB6E3EEE-594F-4EB1-8219-6A316F97EE65}" name="Максимальное кошличество" dataDxfId="27">
-      <calculatedColumnFormula>MAX(Таблица7[[#This Row],[Количество дисков по скорости]],Таблица7[[#This Row],[Количество дисков по объему]])</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" xr3:uid="{7B9E0AE7-DFF6-4A7D-AC36-13C5B3E1093E}" name="Количество дисков на 1 ноде" dataDxfId="26">
-      <calculatedColumnFormula>QUOTIENT(D2,$H$2) + _xlfn.CEILING.MATH(MOD(INT(D2),$H$2)/$H$2)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" xr3:uid="{49B81C8B-9F13-49C6-997E-2A7DFF56A0A2}" name="Количество дисков" dataDxfId="25">
-      <calculatedColumnFormula>Таблица7[[#This Row],[Количество дисков на 1 ноде]]*$H$2</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{E9434E86-EDCB-4627-A674-74F1839A2FC6}" name="Суммарный объем бэкапов (TB)" dataDxfId="8">
+      <calculatedColumnFormula>Таблица6[[#This Row],[Суммарный объем бэкапов (TB)]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{750C3278-2A9B-4925-9B2B-0625F9EB284C}" name="Минимальный объем хранилища на год, ТБ" dataDxfId="6">
+      <calculatedColumnFormula>Таблица3[[#This Row],[Минимальный объем хранилища на год, ТБ]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{4CD8A199-7A19-4CD3-8EF3-6F39CACD9D8B}" name="Стоимость хранения / месяц, Р/мес" dataDxfId="7">
+      <calculatedColumnFormula>B2*$J$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{FACC1920-2D33-4083-AB99-3AF0A400C6E4}" name="Стоимость хранения / месяц, Р/год" dataDxfId="4">
+      <calculatedColumnFormula>Таблица8[[#This Row],[Стоимость хранения / месяц, Р/мес]]*12</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{C4F142FB-0C28-4BE0-87FC-F366D6C6B707}" name="Цена 1 восстановления" dataDxfId="3">
+      <calculatedColumnFormula>(Таблица8[[#This Row],[Минимальный объем хранилища на год, ТБ]]*1024-$K$2)*$L$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{DBF70727-8180-4D7E-95E6-B2818F3EEB59}" name="Цена восстановлений" dataDxfId="1">
+      <calculatedColumnFormula>Таблица8[[#This Row],[Цена 1 восстановления]]*$M$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{D89277AC-4C44-446C-AB02-D1F0F094BA03}" name="Стоимость хранения/год" dataDxfId="0">
+      <calculatedColumnFormula>Таблица8[[#This Row],[Стоимость хранения / месяц, Р/год]]+Таблица8[[#This Row],[Цена восстановлений]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1126,22 +1295,62 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{64B0AF25-7315-40B1-9762-26CBE1B2AF52}" name="Таблица4" displayName="Таблица4" ref="A1:E6" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D410A6A2-ADF3-4601-95DE-0F1DF8F69B2F}" name="Таблица9" displayName="Таблица9" ref="J1:M2" totalsRowShown="0">
+  <autoFilter ref="J1:M2" xr:uid="{D410A6A2-ADF3-4601-95DE-0F1DF8F69B2F}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{8AE78C68-E5BF-4418-BF69-6F8199959907}" name="Ценв 1 ТБ/мес"/>
+    <tableColumn id="2" xr3:uid="{6D45614A-E72F-457A-8320-978ED9606DE0}" name="Неопл объем чтения,ГБ"/>
+    <tableColumn id="3" xr3:uid="{7F5FBE56-3A3E-487A-B343-6B7B27EC0224}" name="Цена чтения, Р/ГБ" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{904B2DE1-96BD-4141-9E6B-570114E244D8}" name="Количество восстановлений/год"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{24CBF245-BDE9-4C57-B274-210639C2127C}" name="Таблица7" displayName="Таблица7" ref="A1:F6" totalsRowShown="0">
+  <autoFilter ref="A1:F6" xr:uid="{24CBF245-BDE9-4C57-B274-210639C2127C}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{C0BE04AD-D800-4036-9197-44872A225E08}" name="Год" dataDxfId="25">
+      <calculatedColumnFormula>A1+1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{2D787ECA-3674-4996-A74B-32A7AC30B58F}" name="Количество дисков по скорости">
+      <calculatedColumnFormula>Таблица5[[#This Row],[Минимальное колическттвол дисков]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{608B01F1-5670-47B4-8A03-52629C853A7D}" name="Количество дисков по объему" dataDxfId="24">
+      <calculatedColumnFormula>Таблица6[[#This Row],[Количество дисков]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{CB6E3EEE-594F-4EB1-8219-6A316F97EE65}" name="Максимальное кошличество" dataDxfId="23">
+      <calculatedColumnFormula>MAX(Таблица7[[#This Row],[Количество дисков по скорости]],Таблица7[[#This Row],[Количество дисков по объему]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{7B9E0AE7-DFF6-4A7D-AC36-13C5B3E1093E}" name="Количество дисков на 1 ноде" dataDxfId="22">
+      <calculatedColumnFormula>QUOTIENT(D2,$H$2) + _xlfn.CEILING.MATH(MOD(INT(D2),$H$2)/$H$2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{49B81C8B-9F13-49C6-997E-2A7DFF56A0A2}" name="Количество дисков" dataDxfId="21">
+      <calculatedColumnFormula>Таблица7[[#This Row],[Количество дисков на 1 ноде]]*$H$2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{64B0AF25-7315-40B1-9762-26CBE1B2AF52}" name="Таблица4" displayName="Таблица4" ref="A1:E6" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16">
   <autoFilter ref="A1:E6" xr:uid="{64B0AF25-7315-40B1-9762-26CBE1B2AF52}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5361C555-84F8-4320-B9BF-F5EE77B58EFB}" name="Год" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{5361C555-84F8-4320-B9BF-F5EE77B58EFB}" name="Год" dataDxfId="15">
       <calculatedColumnFormula>A1+1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4BE1F316-36B0-4029-AA9B-2F60456F020C}" name="Объем горячих данных, ГБ" dataDxfId="3">
+    <tableColumn id="2" xr3:uid="{4BE1F316-36B0-4029-AA9B-2F60456F020C}" name="Объем горячих данных, ГБ" dataDxfId="14">
       <calculatedColumnFormula>Таблица3[[#This Row],[(Рост данных/месяц) в текущий год, ГБ/мес]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BDD9D6A0-DC99-4726-AFC5-BF52D22A7307}" name="Объем теплых данных, ГБ" dataDxfId="2">
+    <tableColumn id="3" xr3:uid="{BDD9D6A0-DC99-4726-AFC5-BF52D22A7307}" name="Объем теплых данных, ГБ" dataDxfId="13">
       <calculatedColumnFormula>B2*11</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{761A234F-4C93-4AE3-BD5F-7F3D3EA47276}" name="Объем холодных данных, ГБ" dataDxfId="1">
+    <tableColumn id="4" xr3:uid="{761A234F-4C93-4AE3-BD5F-7F3D3EA47276}" name="Объем холодных данных, ГБ" dataDxfId="12">
       <calculatedColumnFormula>SUM($C$1:C2) + SUM($B1:B$2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{AEB39C59-6A5D-4FDD-B04F-3733EA889425}" name="Минимальный объем хранилища на год, ГБ" dataDxfId="0">
+    <tableColumn id="5" xr3:uid="{AEB39C59-6A5D-4FDD-B04F-3733EA889425}" name="Минимальный объем хранилища на год, ГБ" dataDxfId="11">
       <calculatedColumnFormula>SUM(B2:D2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1579,8 +1788,8 @@
         <v>13650</v>
       </c>
       <c r="E2">
-        <f>_xlfn.CEILING.MATH(D2/1024,0.1)</f>
-        <v>13.4</v>
+        <f t="shared" ref="E2:E6" si="0">_xlfn.CEILING.MATH(D2/1024,0.01)</f>
+        <v>13.34</v>
       </c>
       <c r="G2">
         <v>10</v>
@@ -1600,7 +1809,7 @@
         <v>1252</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C6" si="0">B3*12</f>
+        <f t="shared" ref="C3:C6" si="1">B3*12</f>
         <v>15024</v>
       </c>
       <c r="D3">
@@ -1608,8 +1817,8 @@
         <v>28674</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E6" si="1">_xlfn.CEILING.MATH(D3/1024,0.1)</f>
-        <v>28.1</v>
+        <f t="shared" si="0"/>
+        <v>28.01</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1622,7 +1831,7 @@
         <v>1378</v>
       </c>
       <c r="C4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16536</v>
       </c>
       <c r="D4">
@@ -1630,8 +1839,8 @@
         <v>45210</v>
       </c>
       <c r="E4">
-        <f t="shared" si="1"/>
-        <v>44.2</v>
+        <f t="shared" si="0"/>
+        <v>44.160000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -1644,7 +1853,7 @@
         <v>1516</v>
       </c>
       <c r="C5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18192</v>
       </c>
       <c r="D5">
@@ -1652,8 +1861,8 @@
         <v>63402</v>
       </c>
       <c r="E5">
-        <f t="shared" si="1"/>
-        <v>62</v>
+        <f t="shared" si="0"/>
+        <v>61.92</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -1666,7 +1875,7 @@
         <v>1668</v>
       </c>
       <c r="C6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20016</v>
       </c>
       <c r="D6">
@@ -1674,8 +1883,8 @@
         <v>83418</v>
       </c>
       <c r="E6">
-        <f t="shared" si="1"/>
-        <v>81.5</v>
+        <f t="shared" si="0"/>
+        <v>81.47</v>
       </c>
     </row>
   </sheetData>
@@ -1992,6 +2201,256 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ACB3484-C46F-4466-B77F-2F98DA0CDA31}">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30.21875" customWidth="1"/>
+    <col min="3" max="3" width="41" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="30.88671875" customWidth="1"/>
+    <col min="15" max="15" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="12">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12">
+        <f>Таблица6[[#This Row],[Суммарный объем бэкапов (TB)]]</f>
+        <v>38.83</v>
+      </c>
+      <c r="C2" s="15">
+        <f>Таблица3[[#This Row],[Минимальный объем хранилища на год, ТБ]]</f>
+        <v>13.34</v>
+      </c>
+      <c r="D2" s="14">
+        <f>B2*$J$2</f>
+        <v>94473.39</v>
+      </c>
+      <c r="E2" s="14">
+        <f>Таблица8[[#This Row],[Стоимость хранения / месяц, Р/мес]]*12</f>
+        <v>1133680.68</v>
+      </c>
+      <c r="F2" s="14">
+        <f>(Таблица8[[#This Row],[Минимальный объем хранилища на год, ТБ]]*1024-$K$2)*$L$2</f>
+        <v>18509.924859616</v>
+      </c>
+      <c r="G2" s="14">
+        <f>Таблица8[[#This Row],[Цена 1 восстановления]]*$M$2</f>
+        <v>37019.849719231999</v>
+      </c>
+      <c r="H2" s="14">
+        <f>Таблица8[[#This Row],[Стоимость хранения / месяц, Р/год]]+Таблица8[[#This Row],[Цена восстановлений]]</f>
+        <v>1170700.5297192319</v>
+      </c>
+      <c r="J2">
+        <v>2433</v>
+      </c>
+      <c r="K2">
+        <v>100</v>
+      </c>
+      <c r="L2" s="16">
+        <v>1.3650226000000001</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="13">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" s="12">
+        <f>Таблица6[[#This Row],[Суммарный объем бэкапов (TB)]]</f>
+        <v>82.61</v>
+      </c>
+      <c r="C3" s="15">
+        <f>Таблица3[[#This Row],[Минимальный объем хранилища на год, ТБ]]</f>
+        <v>28.01</v>
+      </c>
+      <c r="D3" s="14">
+        <f>B3*$J$2</f>
+        <v>200990.13</v>
+      </c>
+      <c r="E3" s="14">
+        <f>Таблица8[[#This Row],[Стоимость хранения / месяц, Р/мес]]*12</f>
+        <v>2411881.56</v>
+      </c>
+      <c r="F3" s="14">
+        <f>(Таблица8[[#This Row],[Минимальный объем хранилища на год, ТБ]]*1024-$K$2)*$L$2</f>
+        <v>39015.403558624006</v>
+      </c>
+      <c r="G3" s="14">
+        <f>Таблица8[[#This Row],[Цена 1 восстановления]]*$M$2</f>
+        <v>78030.807117248012</v>
+      </c>
+      <c r="H3" s="14">
+        <f>Таблица8[[#This Row],[Стоимость хранения / месяц, Р/год]]+Таблица8[[#This Row],[Цена восстановлений]]</f>
+        <v>2489912.367117248</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="12">
+        <f t="shared" ref="A4:A6" si="0">A3+1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" s="12">
+        <f>Таблица6[[#This Row],[Суммарный объем бэкапов (TB)]]</f>
+        <v>130.78</v>
+      </c>
+      <c r="C4" s="15">
+        <f>Таблица3[[#This Row],[Минимальный объем хранилища на год, ТБ]]</f>
+        <v>44.160000000000004</v>
+      </c>
+      <c r="D4" s="14">
+        <f>B4*$J$2</f>
+        <v>318187.74</v>
+      </c>
+      <c r="E4" s="14">
+        <f>Таблица8[[#This Row],[Стоимость хранения / месяц, Р/мес]]*12</f>
+        <v>3818252.88</v>
+      </c>
+      <c r="F4" s="14">
+        <f>(Таблица8[[#This Row],[Минимальный объем хранилища на год, ТБ]]*1024-$K$2)*$L$2</f>
+        <v>61589.601308384008</v>
+      </c>
+      <c r="G4" s="14">
+        <f>Таблица8[[#This Row],[Цена 1 восстановления]]*$M$2</f>
+        <v>123179.20261676802</v>
+      </c>
+      <c r="H4" s="14">
+        <f>Таблица8[[#This Row],[Стоимость хранения / месяц, Р/год]]+Таблица8[[#This Row],[Цена восстановлений]]</f>
+        <v>3941432.0826167678</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="12">
+        <f>Таблица6[[#This Row],[Суммарный объем бэкапов (TB)]]</f>
+        <v>183.77</v>
+      </c>
+      <c r="C5" s="15">
+        <f>Таблица3[[#This Row],[Минимальный объем хранилища на год, ТБ]]</f>
+        <v>61.92</v>
+      </c>
+      <c r="D5" s="14">
+        <f>B5*$J$2</f>
+        <v>447112.41000000003</v>
+      </c>
+      <c r="E5" s="14">
+        <f>Таблица8[[#This Row],[Стоимость хранения / месяц, Р/мес]]*12</f>
+        <v>5365348.92</v>
+      </c>
+      <c r="F5" s="14">
+        <f>(Таблица8[[#This Row],[Минимальный объем хранилища на год, ТБ]]*1024-$K$2)*$L$2</f>
+        <v>86414.229917408011</v>
+      </c>
+      <c r="G5" s="14">
+        <f>Таблица8[[#This Row],[Цена 1 восстановления]]*$M$2</f>
+        <v>172828.45983481602</v>
+      </c>
+      <c r="H5" s="14">
+        <f>Таблица8[[#This Row],[Стоимость хранения / месяц, Р/год]]+Таблица8[[#This Row],[Цена восстановлений]]</f>
+        <v>5538177.3798348159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="12">
+        <f>Таблица6[[#This Row],[Суммарный объем бэкапов (TB)]]</f>
+        <v>242.05</v>
+      </c>
+      <c r="C6" s="15">
+        <f>Таблица3[[#This Row],[Минимальный объем хранилища на год, ТБ]]</f>
+        <v>81.47</v>
+      </c>
+      <c r="D6" s="14">
+        <f>B6*$J$2</f>
+        <v>588907.65</v>
+      </c>
+      <c r="E6" s="14">
+        <f>Таблица8[[#This Row],[Стоимость хранения / месяц, Р/мес]]*12</f>
+        <v>7066891.8000000007</v>
+      </c>
+      <c r="F6" s="14">
+        <f>(Таблица8[[#This Row],[Минимальный объем хранилища на год, ТБ]]*1024-$K$2)*$L$2</f>
+        <v>113740.89035132801</v>
+      </c>
+      <c r="G6" s="14">
+        <f>Таблица8[[#This Row],[Цена 1 восстановления]]*$M$2</f>
+        <v>227481.78070265602</v>
+      </c>
+      <c r="H6" s="14">
+        <f>Таблица8[[#This Row],[Стоимость хранения / месяц, Р/год]]+Таблица8[[#This Row],[Цена восстановлений]]</f>
+        <v>7294373.5807026569</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26B6F34D-1497-4D8C-B6A8-3FF20E1409AC}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2169,7 +2628,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8B68499-B79D-4218-83FE-5399BEA3F19E}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2311,7 +2770,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34FB1CD2-564E-4E39-AEA0-5726DAC2266A}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
